--- a/doc/TestCase.xlsx
+++ b/doc/TestCase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\5240063-VYKTY-DATN-Selenium-BookingHub\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT\2026\5240063-VYKTY-DATN-Selenium-BookingHub\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E89DBD5-35CF-4334-8B05-9E4D455179C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54FA6E3-424A-4DD1-9C37-24A6AB24C66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EF51438B-56DF-448F-81DF-EB7815EF9335}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF51438B-56DF-448F-81DF-EB7815EF9335}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="323">
   <si>
     <t>STT</t>
   </si>
@@ -1132,6 +1132,33 @@
   </si>
   <si>
     <t>Tìm kiếm chuyến thành công</t>
+  </si>
+  <si>
+    <t>Chức năng</t>
+  </si>
+  <si>
+    <t>Trang chủ</t>
+  </si>
+  <si>
+    <t>Tìm chuyến</t>
+  </si>
+  <si>
+    <t>Đặt vé</t>
+  </si>
+  <si>
+    <t>Đăng nhập</t>
+  </si>
+  <si>
+    <t>Vé của tôi</t>
+  </si>
+  <si>
+    <t>Thanh toán</t>
+  </si>
+  <si>
+    <t>Thông tin cá nhân</t>
+  </si>
+  <si>
+    <t>Đăng ký</t>
   </si>
 </sst>
 </file>
@@ -1226,9 +1253,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1266,7 +1293,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1372,7 +1399,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1514,7 +1541,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1522,1634 +1549,1878 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EEB8052-C907-4F01-8C28-426F43D833C5}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="74.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="74.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G2" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G3" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G4" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G5" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G7" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G8" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G9" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G10" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G11" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G12" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G17" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G18" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G19" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G22" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G23" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G31" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G32" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G33" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G34" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G35" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G36" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G37" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G38" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G39" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G40" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G41" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G42" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G43" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G44" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="G45" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="G46" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="G47" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>48</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G48" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G49" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>50</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G50" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>51</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G51" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F52" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G52" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>53</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G53" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G54" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G55" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>56</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G56" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G57" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>58</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="G58" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>59</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G59" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>60</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G60" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>61</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G61" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>62</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F62" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G62" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>63</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G63" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>64</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F64" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G64" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>65</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G65" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>66</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G66" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>67</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F67" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G67" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>68</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F68" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G68" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>69</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="F69" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F69" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G69" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>70</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F70" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G70" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>71</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F71" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G71" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>72</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="F72" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G72" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>73</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F73" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G73" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>74</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="F74" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F74" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G74" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>75</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F75" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="G75" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>76</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F76" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G76" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>77</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F77" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G77" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>78</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F78" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G78" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>79</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F79" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G79" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>80</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="G80" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="G81" s="5" t="s">
         <v>97</v>
       </c>
     </row>
